--- a/data/checklists/nba/1993-94-Topps-Basketball.xlsx
+++ b/data/checklists/nba/1993-94-Topps-Basketball.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D393"/>
+  <dimension ref="A1:D820"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7494,6 +7494,7668 @@
       </c>
       <c r="D393" t="inlineStr"/>
     </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>Sean Elliott</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>Black Gold</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr"/>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>Dennis Scott</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>Black Gold</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr"/>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>Kenny Anderson</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>New Jersey Nets</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>Black Gold</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr"/>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>Alonzo Mourning</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>Black Gold</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr"/>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>Glen Rice</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Miami Heat</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>Black Gold</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr"/>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>Billy Owens</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>Black Gold</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr"/>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>Jim Jackson</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Dallas Mavericks</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>Black Gold</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr"/>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>Derrick Coleman</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>New Jersey Nets</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>Black Gold</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr"/>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>Larry Johnson</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>Black Gold</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr"/>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>Gary Payton</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Seattle SuperSonics</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>Black Gold</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr"/>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>Christian Laettner</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>Black Gold</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr"/>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>Dikembe Mutombo</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>Black Gold</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr"/>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>Mahmoud Abdul-Rauf</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>Black Gold</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr"/>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>Isaiah Rider</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>Black Gold</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr"/>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>Steve Smith</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>Miami Heat</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>Black Gold</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr"/>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>LaPhonso Ellis</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>Black Gold</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr"/>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>Danny Ferry</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>Black Gold</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr"/>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>Shaquille O'Neal</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>Black Gold</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr"/>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>Anfernee Hardaway</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>Black Gold</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr"/>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>J.R. Reid</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>Black Gold</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr"/>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>Shawn Bradley</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>Black Gold</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr"/>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>Pervis Ellison</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>Washington Bullets</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>Black Gold</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr"/>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>Chris Webber</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>Black Gold</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr"/>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>Jamal Mashburn</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>Dallas Mavericks</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>Black Gold</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr"/>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>Kendall Gill</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>Seattle SuperSonics</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>Black Gold</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr"/>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>Winner A: 1-13 RDM</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr"/>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>Black Gold Winners Redemptions</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr"/>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>Winner B: 14-25 RDM</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr"/>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>Black Gold Winners Redemptions</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr"/>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>Winner A/B: 1-25 RDM</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr"/>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>Black Gold Winners Redemptions</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr"/>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>Certified Winner A: 1-13 CL, UER, EXCH UER: #13 "Abdul-Rouf"</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr"/>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>Black Gold Winners Redeemed/Exchange</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr"/>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>Certified Winner B: 14-25 CL, EXCH</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr"/>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>Black Gold Winners Redeemed/Exchange</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr"/>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>Certified Winner A/B: 1-25 CL, EXCH</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr"/>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>Black Gold Winners Redeemed/Exchange</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr"/>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>Charles Barkley</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>Gold - HL</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr"/>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>Hakeem Olajuwon</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>Gold - HL</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr"/>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>Shaquille O'Neal</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>Gold - HL</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr"/>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>Mahmoud Abdul-Rauf</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>Gold - HL</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr"/>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>Clifford Robinson</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>Gold - HL</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr"/>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>Donald Hodge</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>Dallas Mavericks</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr"/>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>Victor Alexander</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr"/>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>Chris Morris</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>New Jersey Nets</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr"/>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>Muggsy Bogues</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr"/>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>Steve Smith</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>Miami Heat</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>Gold - UER</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr"/>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>Dave Johnson</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr"/>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>Tom Gugliotta</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>Washington Bullets</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr"/>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>Doug Edwards</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>Gold - DPK</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr"/>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>Vlade Divac</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr"/>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>Corie Blount</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr"/>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>Derek Harper</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>Dallas Mavericks</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr"/>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>Matt Bullard</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr"/>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>Terry Catledge</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>Gold - UER</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr"/>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>Mark Eaton</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>Utah Jazz</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr"/>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>Mark Jackson</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>Los Angeles Clippers</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr"/>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>Terry Mills</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr"/>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>Johnny Dawkins</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr"/>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>Michael Jordan</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr"/>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>Rick Fox</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr"/>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>Charles Oakley</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr"/>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>Derrick McKey</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>Seattle SuperSonics</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr"/>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>Christian Laettner</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr"/>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>Todd Day</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>Milwaukee Bucks</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr"/>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>Danny Ferry</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr"/>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>Kevin Johnson</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr"/>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>Vinny Del Negro</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr"/>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>Kevin Brooks</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr"/>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>Pete Chilcutt</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>Sacramento Kings</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr"/>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>Larry Stewart</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>Washington Bullets</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr"/>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>Dave Jamerson</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr"/>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>Sidney Green</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr"/>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>J.R. Reid</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr"/>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>Jim Jackson</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>Dallas Mavericks</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr"/>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>Micheal Williams</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>Gold - UER</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr"/>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>Rex Walters</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>New Jersey Nets</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>Gold - DPK</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr"/>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>Shawn Bradley</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>Gold - DPK</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr"/>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>Jon Koncak</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr"/>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>Byron Houston</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr"/>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>Brian Shaw</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>Miami Heat</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr"/>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>Bill Cartwright</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr"/>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>Jerome Kersey</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr"/>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>Danny Schayes</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>Milwaukee Bucks</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr"/>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>Olden Polynice</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr"/>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>Anthony Peeler</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr"/>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>Nick Anderson</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>Gold - 50P</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr"/>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>David Benoit</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>Utah Jazz</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr"/>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>David Robinson</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>Gold - 50P</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr"/>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>Greg Kite</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr"/>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>Gerald Paddio</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>Seattle SuperSonics</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr"/>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>Don MacLean</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>Washington Bullets</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr"/>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>Randy Woods</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>Los Angeles Clippers</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr"/>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>Reggie Miller</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>Indiana Pacers</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>Gold - 50P</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr"/>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>Kevin Gamble</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr"/>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>Sean Green</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>Indiana Pacers</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr"/>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>Jeff Hornacek</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr"/>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>John Starks</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr"/>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>Gerald Wilkins</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr"/>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>Jim Les</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>Sacramento Kings</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr"/>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>Michael Jordan</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>Gold - 50P</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr"/>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>Alvin Robertson</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr"/>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>Tim Kempton</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr"/>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>Bryant Stith</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr"/>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>Jeff Turner</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr"/>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>Malik Sealy</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>Indiana Pacers</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr"/>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>Dell Curry</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr"/>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>Brent Price</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>Washington Bullets</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr"/>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>Kevin Lynch</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr"/>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>Bimbo Coles</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>Miami Heat</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr"/>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>Larry Nance</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr"/>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>Luther Wright</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>Utah Jazz</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>Gold - DPK</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr"/>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>Willie Anderson</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr"/>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>Dennis Rodman</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr"/>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>Anthony Mason</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr"/>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>Chris Gatling</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr"/>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>Antoine Carr</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr"/>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>Kevin Willis</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr"/>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>Thurl Bailey</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr"/>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>Reggie Williams</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr"/>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>Rod Strickland</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr"/>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>Rolando Blackman</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr"/>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>Bobby Hurley</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>Sacramento Kings</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>Gold - DPK</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr"/>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>Jeff Malone</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>Utah Jazz</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr"/>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>James Worthy</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr"/>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>Alaa Abdelnaby</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr"/>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>Duane Ferrell</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr"/>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>Anthony Avent</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>Milwaukee Bucks</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr"/>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>Scottie Pippen</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr"/>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>Ricky Pierce</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>Seattle SuperSonics</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr"/>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>P.J. Brown</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>New Jersey Nets</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr"/>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>Jeff Grayer</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr"/>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>Jerrod Mustaf</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr"/>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>Elmore Spencer</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>Los Angeles Clippers</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr"/>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>Walt Williams</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>Sacramento Kings</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr"/>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>Otis Thorpe</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr"/>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>Patrick Ewing</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>Gold - All-Star</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr"/>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>Michael Jordan</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>Gold - All-Star</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr"/>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>John Stockton</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>Utah Jazz</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>Gold - All-Star</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr"/>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>Dominique Wilkins</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>Gold - All-Star</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr"/>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>Charles Barkley</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>Gold - All-Star</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr"/>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>Lee Mayberry</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>Milwaukee Bucks</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr"/>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>James Edwards</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>Gold - UER</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr"/>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>Scott Brooks</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr"/>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>John Battle</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr"/>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>Kenny Gattison</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr"/>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>Pooh Richardson</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>Indiana Pacers</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr"/>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>Rony Seikaly</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>Miami Heat</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr"/>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>Mahmoud Abdul-Rauf</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr"/>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>Nick Anderson</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr"/>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>Gundars Vetra</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr"/>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>Joe Dumars</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>Gold - All-Star</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr"/>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>Hakeem Olajuwon</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>Gold - All-Star</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr"/>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>Scottie Pippen</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>Gold - All-Star</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr"/>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>Mark Price</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>Gold - All-Star</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr"/>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>Karl Malone</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>Utah Jazz</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>Gold - All-Star</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr"/>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>Michael Cage</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>Seattle SuperSonics</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr"/>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>Ed Pinckney</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr"/>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>Jay Humphries</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>Utah Jazz</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr"/>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>Dale Davis</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>Indiana Pacers</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr"/>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>Sean Rooks</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>Dallas Mavericks</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr"/>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>Mookie Blaylock</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr"/>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>Buck Williams</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr"/>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>John Williams</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>Los Angeles Clippers</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr"/>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>Stacey King</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr"/>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>Tim Perry</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr"/>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>Tim Hardaway</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>Gold - All-Star</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr"/>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>Larry Johnson</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>Gold - All-Star</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr"/>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>Detlef Schrempf</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>Indiana Pacers</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>Gold - All-Star</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr"/>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>Reggie Miller</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>Indiana Pacers</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>Gold - All-Star</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr"/>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>Shaquille O'Neal</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>Gold - All-Star</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr"/>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>Dale Ellis</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr"/>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>Duane Causwell</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>Sacramento Kings</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr"/>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>Rumeal Robinson</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>New Jersey Nets</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr"/>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>Billy Owens</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr"/>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>Malcolm Mackey</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>Gold - DPK</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr"/>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>Vernon Maxwell</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr"/>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>LaPhonso Ellis</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr"/>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>Robert Parish</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr"/>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>LaBradford Smith</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>Washington Bullets</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr"/>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>Charles Smith</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr"/>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>Terry Porter</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr"/>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>Elden Campbell</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr"/>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>Bill Laimbeer</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr"/>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>Chris Mills</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>Gold - DPK</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr"/>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>Brad Lohaus</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>Milwaukee Bucks</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr"/>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>Jim Jackson</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>Dallas Mavericks</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>Gold - ART</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr"/>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>Tom Gugliotta</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>Washington Bullets</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>Gold - ART</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr"/>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>Shaquille O'Neal</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>Gold - ART</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr"/>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>Latrell Sprewell</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>Gold - ART</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr"/>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>Walt Williams</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>Sacramento Kings</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>Gold - ART</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr"/>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>Gary Payton</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>Seattle SuperSonics</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr"/>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>Orlando Woolridge</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>Milwaukee Bucks</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr"/>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>Adam Keefe</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr"/>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>Calbert Cheaney</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>Washington Bullets</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>Gold - DPK</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr"/>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>Rick Mahorn</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>New Jersey Nets</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr"/>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>Robert Horry</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr"/>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>John Salley</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>Miami Heat</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr"/>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>Sam Mitchell</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>Indiana Pacers</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr"/>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>Stanley Roberts</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>Los Angeles Clippers</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr"/>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>Clarence Weatherspoon</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr"/>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>Anthony Bowie</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr"/>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>Derrick Coleman</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>New Jersey Nets</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr"/>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>Negele Knight</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr"/>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>Marlon Maxey</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr"/>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>Spud Webb</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>Sacramento Kings</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr"/>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>Alonzo Mourning</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr"/>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>Ervin Johnson</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>Seattle SuperSonics</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>Gold - DPK</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr"/>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>Sedale Threatt</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr"/>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>Mark Macon</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr"/>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>B.J. Armstrong</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr"/>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>Harold Miner</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>Miami Heat</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>Gold - ART</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr"/>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>Anthony Peeler</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>Gold - ART</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr"/>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>Alonzo Mourning</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>Gold - ART</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr"/>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>Christian Laettner</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>Gold - ART</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr"/>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>Clarence Weatherspoon</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>Gold - ART</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr"/>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>Dee Brown</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr"/>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>Shaquille O'Neal</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr"/>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>Loy Vaught</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>Los Angeles Clippers</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr"/>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>Terrell Brandon</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr"/>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>Lionel Simmons</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>Sacramento Kings</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr"/>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>Mark Aguirre</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr"/>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>Danny Ainge</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr"/>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>Reggie Miller</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>Indiana Pacers</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr"/>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>Terry Davis</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>Dallas Mavericks</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr"/>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>Mark Bryant</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr"/>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>Tyrone Corbin</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>Utah Jazz</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr"/>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>Chris Mullin</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr"/>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>Johnny Newman</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr"/>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>Doug West</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr"/>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>Keith Askins</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>Miami Heat</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr"/>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>Bo Kimble</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr"/>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>Sean Elliott</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr"/>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>David Wingate</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>Gold - Checklist replacement</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr"/>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>Frank Johnson</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>Gold - Checklist replacement</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr"/>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>Michael Jordan</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>Gold - RPM</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr"/>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>Patrick Ewing</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>Gold - FPM</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr"/>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>John Stockton</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>Utah Jazz</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>Gold - FPM</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr"/>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>Shawn Kemp</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>Seattle SuperSonics</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>Gold - FPM</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr"/>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>Mark Price</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>Gold - FPM</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr"/>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>Charles Barkley</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>Gold - FPM</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr"/>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>Hakeem Olajuwon</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>Gold - FPM</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr"/>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>Clyde Drexler</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>Gold - FPM</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr"/>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>Kevin Johnson</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>Gold - FPM</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr"/>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>John Starks</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>Gold - FPM</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr"/>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>Chris Mullin</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>Gold - FPM</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr"/>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>Doc Rivers</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr"/>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>Kenny Walker</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>Washington Bullets</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr"/>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>Doug Christie</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr"/>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>James Robinson</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>Gold - DPK</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr"/>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>Larry Krystkowiak</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr"/>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>Manute Bol</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>Miami Heat</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr"/>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>Carl Herrera</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr"/>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>Paul Graham</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr"/>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>Jud Buechler</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr"/>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>Mike Brown</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr"/>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>Tom Chambers</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>Utah Jazz</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr"/>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>Kendall Gill</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>Seattle SuperSonics</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr"/>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>Kenny Anderson</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>New Jersey Nets</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr"/>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>Larry Johnson</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr"/>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>Chris Webber</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>Gold - DPK</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr"/>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>Randy White</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>Dallas Mavericks</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr"/>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>Rik Smits</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>Indiana Pacers</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr"/>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>A.C. Green</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr"/>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>David Robinson</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr"/>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>Sean Elliott</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr"/>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>Gary Grant</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>Los Angeles Clippers</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr"/>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>Dana Barros</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr"/>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>Bobby Hurley</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>Sacramento Kings</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>Gold - DPK</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr"/>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>Blue Edwards</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>Milwaukee Bucks</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr"/>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>Tom Hammonds</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr"/>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>Pete Myers</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr"/>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>Acie Earl</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>Gold - DPK</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr"/>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>Tony Smith</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr"/>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>Bill Wennington</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr"/>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>Andrew Lang</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr"/>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>Ervin Johnson</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>Seattle SuperSonics</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>Gold - DPK</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr"/>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>Byron Scott</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>Indiana Pacers</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr"/>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>Eddie Johnson</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr"/>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>Anthony Bonner</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr"/>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>Luther Wright</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>Utah Jazz</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>Gold - DPK</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr"/>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>LaSalle Thompson</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>Indiana Pacers</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr"/>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>Harold Miner</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr">
+        <is>
+          <t>Miami Heat</t>
+        </is>
+      </c>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr"/>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>Chris Smith</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr"/>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>John Williams</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr"/>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>Clyde Drexler</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr"/>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>Calbert Cheaney</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr">
+        <is>
+          <t>Washington Bullets</t>
+        </is>
+      </c>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>Gold - DPK</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr"/>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>Avery Johnson</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr"/>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>Steve Kerr</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr"/>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>Warren Kidd</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr"/>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>Wayman Tisdale</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>Sacramento Kings</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr"/>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>Bob Martin</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>Los Angeles Clippers</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr"/>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>Popeye Jones</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>Dallas Mavericks</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr"/>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>Jimmy Oliver</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr"/>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>Kevin Edwards</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>New Jersey Nets</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr"/>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>Dan Majerle</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr"/>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>Jon Barry</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>Milwaukee Bucks</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr"/>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>Allan Houston</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>Gold - DPK</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr"/>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>Dikembe Mutombo</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr"/>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>Sleepy Floyd</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr"/>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>George Lynch</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>Gold - DPK</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr"/>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>Stacey Augmon</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>Gold - UER</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr"/>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>Hakeem Olajuwon</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr"/>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>Scott Skiles</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr"/>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>Detlef Schrempf</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>Seattle SuperSonics</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr"/>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>Brian Davis</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr"/>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>Tracy Murray</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr"/>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>Gheorghe Muresan</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>Washington Bullets</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>Gold - DPK</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr"/>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>Terry Dehere</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>Los Angeles Clippers</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>Gold - DPK</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr"/>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>Terry Cummings</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr"/>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>Keith Jennings</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr"/>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>Tyrone Hill</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D699" t="inlineStr"/>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>Hersey Hawkins</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr"/>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>Grant Long</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>Miami Heat</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr"/>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>Herb Williams</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr"/>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>Karl Malone</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>Utah Jazz</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr"/>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>Mitch Richmond</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>Sacramento Kings</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D704" t="inlineStr"/>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>Derek Strong</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>Milwaukee Bucks</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr"/>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>Dino Radja</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr"/>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>Jack Haley</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr"/>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>Derek Harper</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D708" t="inlineStr"/>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>Dwayne Schintzius</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>New Jersey Nets</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr"/>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>Michael Curry</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr"/>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>Rodney Rogers</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>Gold - DPK</t>
+        </is>
+      </c>
+      <c r="D711" t="inlineStr"/>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>Horace Grant</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr"/>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>Oliver Miller</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr"/>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>Luc Longley</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D714" t="inlineStr"/>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>Walter Bond</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>Utah Jazz</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr"/>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>Dominique Wilkins</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr"/>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>Vern Fleming</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>Indiana Pacers</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr"/>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>Mark Price</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr"/>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>Mark Aguirre</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr">
+        <is>
+          <t>Los Angeles Clippers</t>
+        </is>
+      </c>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr"/>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>Shawn Kemp</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr">
+        <is>
+          <t>Seattle SuperSonics</t>
+        </is>
+      </c>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr"/>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>Pervis Ellison</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr">
+        <is>
+          <t>Washington Bullets</t>
+        </is>
+      </c>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr"/>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>Josh Grant</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>Gold - DPK</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr"/>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>Scott Burrell</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>Gold - DPK</t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr"/>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>Patrick Ewing</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr"/>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>Sam Cassell</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>Gold - DPK</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr"/>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>Nick Van Exel</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>Gold - DPK</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr"/>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>Clifford Robinson</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr"/>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>Frank Johnson</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr"/>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>Matt Geiger</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr">
+        <is>
+          <t>Miami Heat</t>
+        </is>
+      </c>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D729" t="inlineStr"/>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>Vin Baker</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr">
+        <is>
+          <t>Milwaukee Bucks</t>
+        </is>
+      </c>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>Gold - DPK</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr"/>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>Benoit Benjamin</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>New Jersey Nets</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr"/>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>Shawn Bradley</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>Gold - DPK</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr"/>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>Chris Whitney</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>Gold - DPK</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr"/>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>Eric Riley</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>Gold - DPK</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr"/>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>Isiah Thomas</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr"/>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>Jamal Mashburn</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>Dallas Mavericks</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>Gold - DPK</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr"/>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>Xavier McDaniel</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr"/>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>Mike Peplowski</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>Sacramento Kings</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>Gold - DPK</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr"/>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>Darnell Mee</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>Gold - DPK</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr"/>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>Toni Kukoc</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr"/>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>Felton Spencer</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>Utah Jazz</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D741" t="inlineStr"/>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>Sam Bowie</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D742" t="inlineStr"/>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>Mario Elie</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D743" t="inlineStr"/>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>Tim Hardaway</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr"/>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>Ken Norman</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr">
+        <is>
+          <t>Milwaukee Bucks</t>
+        </is>
+      </c>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr"/>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>Isaiah Rider</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>Gold - DPK</t>
+        </is>
+      </c>
+      <c r="D746" t="inlineStr"/>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>Rex Chapman</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>Washington Bullets</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D747" t="inlineStr"/>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>Dennis Rodman</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D748" t="inlineStr"/>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>Derrick McKey</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>Indiana Pacers</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D749" t="inlineStr"/>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>Corie Blount</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>Gold - DPK</t>
+        </is>
+      </c>
+      <c r="D750" t="inlineStr"/>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>Lafayette Lever</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>Dallas Mavericks</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D751" t="inlineStr"/>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>Ron Harper</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>Los Angeles Clippers</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D752" t="inlineStr"/>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>Eric Anderson</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D753" t="inlineStr"/>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>Armon Gilliam</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>New Jersey Nets</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D754" t="inlineStr"/>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>Lindsey Hunter</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>Gold - DPK</t>
+        </is>
+      </c>
+      <c r="D755" t="inlineStr"/>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>Eric Leckner</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D756" t="inlineStr"/>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>Chris Corchiani</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D757" t="inlineStr"/>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>Anfernee Hardaway</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>Gold - DPK</t>
+        </is>
+      </c>
+      <c r="D758" t="inlineStr"/>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>Randy Brown</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>Sacramento Kings</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D759" t="inlineStr"/>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>Sam Perkins</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>Seattle SuperSonics</t>
+        </is>
+      </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D760" t="inlineStr"/>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>Glen Rice</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>Miami Heat</t>
+        </is>
+      </c>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D761" t="inlineStr"/>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>Orlando Woolridge</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D762" t="inlineStr"/>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>Mike Gminski</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D763" t="inlineStr"/>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>Latrell Sprewell</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D764" t="inlineStr"/>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>Harvey Grant</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D765" t="inlineStr"/>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>Doug Smith</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>Dallas Mavericks</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D766" t="inlineStr"/>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>Kevin Duckworth</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>Washington Bullets</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D767" t="inlineStr"/>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>Cedric Ceballos</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D768" t="inlineStr"/>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>Chuck Person</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr">
+        <is>
+          <t>Minnesota Timberwolves</t>
+        </is>
+      </c>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D769" t="inlineStr"/>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>Scott Haskin</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr">
+        <is>
+          <t>Indiana Pacers</t>
+        </is>
+      </c>
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>Gold - DPK</t>
+        </is>
+      </c>
+      <c r="D770" t="inlineStr"/>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>Frank Brickowski</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr">
+        <is>
+          <t>Milwaukee Bucks</t>
+        </is>
+      </c>
+      <c r="C771" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D771" t="inlineStr"/>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>Scott Williams</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="C772" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D772" t="inlineStr"/>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>Brad Daugherty</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr">
+        <is>
+          <t>Cleveland Cavaliers</t>
+        </is>
+      </c>
+      <c r="C773" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D773" t="inlineStr"/>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>Willie Burton</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr">
+        <is>
+          <t>Miami Heat</t>
+        </is>
+      </c>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D774" t="inlineStr"/>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>Joe Dumars</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr">
+        <is>
+          <t>Detroit Pistons</t>
+        </is>
+      </c>
+      <c r="C775" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D775" t="inlineStr"/>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>Craig Ehlo</t>
+        </is>
+      </c>
+      <c r="B776" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="C776" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D776" t="inlineStr"/>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>Lucious Harris</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr">
+        <is>
+          <t>Dallas Mavericks</t>
+        </is>
+      </c>
+      <c r="C777" t="inlineStr">
+        <is>
+          <t>Gold - DPK</t>
+        </is>
+      </c>
+      <c r="D777" t="inlineStr"/>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>Danny Manning</t>
+        </is>
+      </c>
+      <c r="B778" t="inlineStr">
+        <is>
+          <t>Los Angeles Clippers</t>
+        </is>
+      </c>
+      <c r="C778" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D778" t="inlineStr"/>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>Litterial Green</t>
+        </is>
+      </c>
+      <c r="B779" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="C779" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D779" t="inlineStr"/>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>John Stockton</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr">
+        <is>
+          <t>Utah Jazz</t>
+        </is>
+      </c>
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D780" t="inlineStr"/>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>Nate McMillan</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>Seattle SuperSonics</t>
+        </is>
+      </c>
+      <c r="C781" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D781" t="inlineStr"/>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>Greg Graham</t>
+        </is>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="C782" t="inlineStr">
+        <is>
+          <t>Gold - DPK</t>
+        </is>
+      </c>
+      <c r="D782" t="inlineStr"/>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>Rex Walters</t>
+        </is>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>New Jersey Nets</t>
+        </is>
+      </c>
+      <c r="C783" t="inlineStr">
+        <is>
+          <t>Gold - DPK</t>
+        </is>
+      </c>
+      <c r="D783" t="inlineStr"/>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>Lloyd Daniels</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="C784" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D784" t="inlineStr"/>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>Antonio Harvey</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>Los Angeles Lakers</t>
+        </is>
+      </c>
+      <c r="C785" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D785" t="inlineStr"/>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>Brian Williams</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="C786" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D786" t="inlineStr"/>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>LeRon Ellis</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="C787" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D787" t="inlineStr"/>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>Chris Dudley</t>
+        </is>
+      </c>
+      <c r="B788" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="C788" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D788" t="inlineStr"/>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>Hubert Davis</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="C789" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D789" t="inlineStr"/>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>Evers Burns</t>
+        </is>
+      </c>
+      <c r="B790" t="inlineStr">
+        <is>
+          <t>Sacramento Kings</t>
+        </is>
+      </c>
+      <c r="C790" t="inlineStr">
+        <is>
+          <t>Gold - DPK</t>
+        </is>
+      </c>
+      <c r="D790" t="inlineStr"/>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>Sherman Douglas</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr">
+        <is>
+          <t>Boston Celtics</t>
+        </is>
+      </c>
+      <c r="C791" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D791" t="inlineStr"/>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>Sarunas Marciulionis</t>
+        </is>
+      </c>
+      <c r="B792" t="inlineStr">
+        <is>
+          <t>Golden State Warriors</t>
+        </is>
+      </c>
+      <c r="C792" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D792" t="inlineStr"/>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>Tom Tolbert</t>
+        </is>
+      </c>
+      <c r="B793" t="inlineStr">
+        <is>
+          <t>Los Angeles Clippers</t>
+        </is>
+      </c>
+      <c r="C793" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D793" t="inlineStr"/>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>Robert Pack</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr">
+        <is>
+          <t>Denver Nuggets</t>
+        </is>
+      </c>
+      <c r="C794" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D794" t="inlineStr"/>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>Michael Adams</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr">
+        <is>
+          <t>Washington Bullets</t>
+        </is>
+      </c>
+      <c r="C795" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D795" t="inlineStr"/>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>Negele Knight</t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="C796" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D796" t="inlineStr"/>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>Charles Barkley</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="C797" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D797" t="inlineStr"/>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>Bryon Russell</t>
+        </is>
+      </c>
+      <c r="B798" t="inlineStr">
+        <is>
+          <t>Utah Jazz</t>
+        </is>
+      </c>
+      <c r="C798" t="inlineStr">
+        <is>
+          <t>Gold - DPK</t>
+        </is>
+      </c>
+      <c r="D798" t="inlineStr"/>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>Greg Anthony</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="C799" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D799" t="inlineStr"/>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>Ken Williams</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr">
+        <is>
+          <t>Indiana Pacers</t>
+        </is>
+      </c>
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D800" t="inlineStr"/>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>John Paxson</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="C801" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D801" t="inlineStr"/>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>Corey Gaines</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="C802" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D802" t="inlineStr"/>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>Eric Murdock</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr">
+        <is>
+          <t>Milwaukee Bucks</t>
+        </is>
+      </c>
+      <c r="C803" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D803" t="inlineStr"/>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>Kevin Thompson</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr">
+        <is>
+          <t>Portland Trail Blazers</t>
+        </is>
+      </c>
+      <c r="C804" t="inlineStr">
+        <is>
+          <t>Gold - DPK</t>
+        </is>
+      </c>
+      <c r="D804" t="inlineStr"/>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>Moses Malone</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr">
+        <is>
+          <t>Philadelphia 76ers</t>
+        </is>
+      </c>
+      <c r="C805" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D805" t="inlineStr"/>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>Kenny Smith</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="C806" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D806" t="inlineStr"/>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>Dennis Scott</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="C807" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="D807" t="inlineStr"/>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>Michael Jordan</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="C808" t="inlineStr">
+        <is>
+          <t>Gold - RSL</t>
+        </is>
+      </c>
+      <c r="D808" t="inlineStr"/>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>Hakeem Olajuwon</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr">
+        <is>
+          <t>Houston Rockets</t>
+        </is>
+      </c>
+      <c r="C809" t="inlineStr">
+        <is>
+          <t>Gold - FSL</t>
+        </is>
+      </c>
+      <c r="D809" t="inlineStr"/>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>Shaquille O'Neal</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr">
+        <is>
+          <t>Orlando Magic</t>
+        </is>
+      </c>
+      <c r="C810" t="inlineStr">
+        <is>
+          <t>Gold - FSL</t>
+        </is>
+      </c>
+      <c r="D810" t="inlineStr"/>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>David Robinson</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr">
+        <is>
+          <t>San Antonio Spurs</t>
+        </is>
+      </c>
+      <c r="C811" t="inlineStr">
+        <is>
+          <t>Gold - FSL</t>
+        </is>
+      </c>
+      <c r="D811" t="inlineStr"/>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>Derrick Coleman</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr">
+        <is>
+          <t>New Jersey Nets</t>
+        </is>
+      </c>
+      <c r="C812" t="inlineStr">
+        <is>
+          <t>Gold - FSL</t>
+        </is>
+      </c>
+      <c r="D812" t="inlineStr"/>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>Karl Malone</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr">
+        <is>
+          <t>Utah Jazz</t>
+        </is>
+      </c>
+      <c r="C813" t="inlineStr">
+        <is>
+          <t>Gold - FSL</t>
+        </is>
+      </c>
+      <c r="D813" t="inlineStr"/>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>Patrick Ewing</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr">
+        <is>
+          <t>New York Knicks</t>
+        </is>
+      </c>
+      <c r="C814" t="inlineStr">
+        <is>
+          <t>Gold - FSL</t>
+        </is>
+      </c>
+      <c r="D814" t="inlineStr"/>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>Scottie Pippen</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="C815" t="inlineStr">
+        <is>
+          <t>Gold - FSL</t>
+        </is>
+      </c>
+      <c r="D815" t="inlineStr"/>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>Dominique Wilkins</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr">
+        <is>
+          <t>Atlanta Hawks</t>
+        </is>
+      </c>
+      <c r="C816" t="inlineStr">
+        <is>
+          <t>Gold - FSL</t>
+        </is>
+      </c>
+      <c r="D816" t="inlineStr"/>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>Charles Barkley</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="C817" t="inlineStr">
+        <is>
+          <t>Gold - FSL</t>
+        </is>
+      </c>
+      <c r="D817" t="inlineStr"/>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>Larry Johnson</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr">
+        <is>
+          <t>Charlotte Hornets</t>
+        </is>
+      </c>
+      <c r="C818" t="inlineStr">
+        <is>
+          <t>Gold - FSL</t>
+        </is>
+      </c>
+      <c r="D818" t="inlineStr"/>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>Will Perdue</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr">
+        <is>
+          <t>Chicago Bulls</t>
+        </is>
+      </c>
+      <c r="C819" t="inlineStr">
+        <is>
+          <t>Gold - Checklist replacement</t>
+        </is>
+      </c>
+      <c r="D819" t="inlineStr"/>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>Mark West</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr">
+        <is>
+          <t>Phoenix Suns</t>
+        </is>
+      </c>
+      <c r="C820" t="inlineStr">
+        <is>
+          <t>Gold - Checklist replacement - Shadow Charles Barkley</t>
+        </is>
+      </c>
+      <c r="D820" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
